--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N94_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N94_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>64.28645721126067</v>
+        <v>10.44654929682986</v>
       </c>
       <c r="D2" t="n">
-        <v>52.1164237056463</v>
+        <v>8.468918852167524</v>
       </c>
       <c r="E2" t="n">
-        <v>17.62212629287072</v>
+        <v>2.863595522591492</v>
       </c>
       <c r="F2" t="n">
-        <v>16.91523606328315</v>
+        <v>2.748725860283511</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>72.621333376598</v>
+        <v>11.80096667369718</v>
       </c>
       <c r="D3" t="n">
-        <v>56.1633332344155</v>
+        <v>9.126541650592518</v>
       </c>
       <c r="E3" t="n">
-        <v>17.62212629287072</v>
+        <v>2.863595522591492</v>
       </c>
       <c r="F3" t="n">
-        <v>16.91523606328315</v>
+        <v>2.748725860283511</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.18182067285044</v>
+        <v>6.692045859338197</v>
       </c>
       <c r="D4" t="n">
-        <v>27.56032900692014</v>
+        <v>4.478553463624523</v>
       </c>
       <c r="E4" t="n">
-        <v>17.62212629287072</v>
+        <v>2.863595522591492</v>
       </c>
       <c r="F4" t="n">
-        <v>16.91523606328315</v>
+        <v>2.748725860283511</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.174106052555</v>
+        <v>4.253292233540188</v>
       </c>
       <c r="D5" t="n">
-        <v>27.35106326826224</v>
+        <v>4.444547781092615</v>
       </c>
       <c r="E5" t="n">
-        <v>17.62212629287072</v>
+        <v>2.863595522591492</v>
       </c>
       <c r="F5" t="n">
-        <v>16.91523606328315</v>
+        <v>2.748725860283511</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.13248113511802</v>
+        <v>4.409028184456678</v>
       </c>
       <c r="D6" t="n">
-        <v>9.160104674436367</v>
+        <v>1.48851700959591</v>
       </c>
       <c r="E6" t="n">
-        <v>17.62212629287072</v>
+        <v>2.863595522591492</v>
       </c>
       <c r="F6" t="n">
-        <v>16.91523606328315</v>
+        <v>2.748725860283511</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.54569529355711</v>
+        <v>4.151175485203031</v>
       </c>
       <c r="D7" t="n">
-        <v>13.54318849580235</v>
+        <v>2.200768130567883</v>
       </c>
       <c r="E7" t="n">
-        <v>17.62212629287072</v>
+        <v>2.863595522591492</v>
       </c>
       <c r="F7" t="n">
-        <v>16.91523606328315</v>
+        <v>2.748725860283511</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>43.6447567801648</v>
+        <v>7.092272976776781</v>
       </c>
       <c r="D8" t="n">
-        <v>19.30336661857093</v>
+        <v>3.136797075517776</v>
       </c>
       <c r="E8" t="n">
-        <v>17.62212629287072</v>
+        <v>2.863595522591492</v>
       </c>
       <c r="F8" t="n">
-        <v>16.91523606328315</v>
+        <v>2.748725860283511</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
